--- a/cuadros/JUNIO/VICTORIA.xlsx
+++ b/cuadros/JUNIO/VICTORIA.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WILRSID I. VILLEGAS</t>
+          <t xml:space="preserve">proveedor </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -524,14 +524,10 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el proveedor cancela una unidad de cerveza de lata por venir averiado en el despacho </t>
+          <t>el proveedor cancela una unidad de cerveza de lata por venir averiado en el despacho</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -539,7 +535,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>COB_152558_0.jpg</t>
+          <t>COB_155456_0.jpg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -549,12 +545,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>INC_152558_0.jpg</t>
+          <t>INC_155456_0.jpg</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ID_20260603152558</t>
+          <t>ID_20260603155456</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/VICTORIA.xlsx
+++ b/cuadros/JUNIO/VICTORIA.xlsx
@@ -524,7 +524,6 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>el proveedor cancela una unidad de cerveza de lata por venir averiado en el despacho</t>
